--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
   <si>
     <t>_id</t>
   </si>
@@ -362,46 +362,28 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>0级链头</t>
-  </si>
-  <si>
-    <t>20001</t>
-  </si>
-  <si>
-    <t>0级链头镯</t>
-  </si>
-  <si>
-    <t>20001,20002</t>
-  </si>
-  <si>
-    <t>0级链头镯戒</t>
-  </si>
-  <si>
-    <t>20001,20002,20003</t>
-  </si>
-  <si>
-    <t>0级链头镯戒腰鞋</t>
-  </si>
-  <si>
-    <t>20001,20002,20003,20004</t>
-  </si>
-  <si>
-    <t>0级链头镯戒腰鞋甲</t>
-  </si>
-  <si>
-    <t>100,100,100,100,10</t>
-  </si>
-  <si>
-    <t>20001,20002,20003,20004,20005</t>
-  </si>
-  <si>
-    <t>0级链头镯戒腰鞋甲剑</t>
+    <t>0级装备</t>
+  </si>
+  <si>
+    <t>400,20,20,20,2,1</t>
+  </si>
+  <si>
+    <t>20001,20002,20003,20004,20005,20006</t>
+  </si>
+  <si>
+    <t>20,400,20,20,2,1</t>
+  </si>
+  <si>
+    <t>20,20,400,20,2,1</t>
+  </si>
+  <si>
+    <t>20,20,20,400,2,1</t>
+  </si>
+  <si>
+    <t>100,100,100,100,5,1</t>
   </si>
   <si>
     <t>100,100,100,100,10,5</t>
-  </si>
-  <si>
-    <t>20001,20002,20003,20004,20005,20006</t>
   </si>
   <si>
     <t>10级技能书</t>
@@ -1570,8 +1552,11 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
+      <c r="G6" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="H6" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:8">
@@ -1579,13 +1564,16 @@
         <v>2002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
+      <c r="G7" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="H7" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -1593,13 +1581,16 @@
         <v>2003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
+      <c r="G8" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="H8" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -1607,13 +1598,16 @@
         <v>2004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
+      <c r="G9" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="H9" s="9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -1621,16 +1615,16 @@
         <v>2005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -1638,16 +1632,16 @@
         <v>2006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1894,13 +1888,13 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1908,16 +1902,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1925,16 +1919,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1942,16 +1936,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1959,16 +1953,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1976,16 +1970,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1993,56 +1987,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2154,16 +2148,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2171,16 +2165,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -2040,6 +2040,7 @@
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
+    <row r="20" customFormat="1" customHeight="1"/>
     <row r="24" s="1" customFormat="1" customHeight="1"/>
     <row r="25" s="1" customFormat="1" customHeight="1"/>
     <row r="26" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="54">
   <si>
     <t>_id</t>
   </si>
@@ -362,28 +362,34 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>0级装备</t>
-  </si>
-  <si>
-    <t>400,20,20,20,2,1</t>
+    <t>1级装备</t>
+  </si>
+  <si>
+    <t>200,30,30,30,2,1</t>
   </si>
   <si>
     <t>20001,20002,20003,20004,20005,20006</t>
   </si>
   <si>
-    <t>20,400,20,20,2,1</t>
-  </si>
-  <si>
-    <t>20,20,400,20,2,1</t>
-  </si>
-  <si>
-    <t>20,20,20,400,2,1</t>
+    <t>30,200,30,30,2,1</t>
+  </si>
+  <si>
+    <t>30,30,200,30,2,1</t>
+  </si>
+  <si>
+    <t>30,30,30,200,2,1</t>
   </si>
   <si>
     <t>100,100,100,100,5,1</t>
   </si>
   <si>
     <t>100,100,100,100,10,5</t>
+  </si>
+  <si>
+    <t>10级装备</t>
+  </si>
+  <si>
+    <t>20007,20008,20009,20010,20011,20012</t>
   </si>
   <si>
     <t>10级技能书</t>
@@ -664,12 +670,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1467,7 +1473,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:H11"/>
+  <dimension ref="C2:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1642,6 +1648,108 @@
       </c>
       <c r="H11" s="9" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:8">
+      <c r="C12" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:8">
+      <c r="C13" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:8">
+      <c r="C14" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:8">
+      <c r="C15" s="1">
+        <v>2010</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:8">
+      <c r="C16" s="1">
+        <v>2011</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:8">
+      <c r="C17" s="1">
+        <v>2012</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1888,13 +1996,13 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1902,16 +2010,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1919,16 +2027,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1936,16 +2044,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1953,16 +2061,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1970,16 +2078,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -1987,56 +2095,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2149,16 +2257,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2166,16 +2274,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -670,12 +670,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2260,7 +2260,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>50</v>
@@ -2277,7 +2277,7 @@
         <v>52</v>
       </c>
       <c r="E7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>50</v>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="70">
   <si>
     <t>_id</t>
   </si>
@@ -392,6 +392,30 @@
     <t>20007,20008,20009,20010,20011,20012</t>
   </si>
   <si>
+    <t>20级装备</t>
+  </si>
+  <si>
+    <t>20013,20014,20015,20016,20017,20018</t>
+  </si>
+  <si>
+    <t>30级装备</t>
+  </si>
+  <si>
+    <t>20019,20020,20021,20022,20023,20024</t>
+  </si>
+  <si>
+    <t>40级装备</t>
+  </si>
+  <si>
+    <t>20025,20026,20027,20028,20029,20030</t>
+  </si>
+  <si>
+    <t>50级装备</t>
+  </si>
+  <si>
+    <t>20031,20032,20033,20034,20035,20036</t>
+  </si>
+  <si>
     <t>10级技能书</t>
   </si>
   <si>
@@ -467,7 +491,7 @@
     <t>40001,40002,40003,40004,40005,40006,40007,40008,40009</t>
   </si>
   <si>
-    <t>小鸡材料</t>
+    <t>落日平原珍宝材料</t>
   </si>
   <si>
     <t>25,3,1</t>
@@ -476,10 +500,34 @@
     <t>50001,50002,50003</t>
   </si>
   <si>
-    <t>小鹿材料</t>
+    <t>幽暗沼泽珍宝材料</t>
   </si>
   <si>
     <t>50004,50005,50006</t>
+  </si>
+  <si>
+    <t>碎石矿场珍宝材料</t>
+  </si>
+  <si>
+    <t>50007,50008,50009</t>
+  </si>
+  <si>
+    <t>枯骨荒漠珍宝材料</t>
+  </si>
+  <si>
+    <t>50010,50011,50012</t>
+  </si>
+  <si>
+    <t>迷雾森林珍宝材料</t>
+  </si>
+  <si>
+    <t>50013,50014,50015</t>
+  </si>
+  <si>
+    <t>熔火地穴珍宝材料</t>
+  </si>
+  <si>
+    <t>50016,50017,50018</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:H17"/>
+  <dimension ref="C2:H41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1750,6 +1798,414 @@
       </c>
       <c r="H17" s="9" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:8">
+      <c r="C18" s="1">
+        <v>2013</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:8">
+      <c r="C19" s="1">
+        <v>2014</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:8">
+      <c r="C20" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:8">
+      <c r="C21" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:8">
+      <c r="C22" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:8">
+      <c r="C23" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:8">
+      <c r="C24" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:8">
+      <c r="C25" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:8">
+      <c r="C26" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:8">
+      <c r="C27" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:8">
+      <c r="C28" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:8">
+      <c r="C29" s="1">
+        <v>2024</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:8">
+      <c r="C30" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:8">
+      <c r="C31" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:8">
+      <c r="C32" s="1">
+        <v>2027</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:8">
+      <c r="C33" s="1">
+        <v>2028</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:8">
+      <c r="C34" s="1">
+        <v>2029</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:8">
+      <c r="C35" s="1">
+        <v>2030</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:8">
+      <c r="C36" s="1">
+        <v>2031</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:8">
+      <c r="C37" s="1">
+        <v>2032</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:8">
+      <c r="C38" s="1">
+        <v>2033</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:8">
+      <c r="C39" s="1">
+        <v>2034</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:8">
+      <c r="C40" s="1">
+        <v>2035</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:8">
+      <c r="C41" s="1">
+        <v>2036</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1996,13 +2452,13 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2010,16 +2466,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2027,16 +2483,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2044,16 +2500,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2061,16 +2517,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2078,16 +2534,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2095,56 +2551,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2173,8 +2629,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="C1:H11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -2257,16 +2713,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2274,16 +2730,84 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>53</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:8">
+      <c r="C8" s="6">
+        <v>5003</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="1">
+        <v>6</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:8">
+      <c r="C9" s="6">
+        <v>5004</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:8">
+      <c r="C10" s="6">
+        <v>5005</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="1">
+        <v>6</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:8">
+      <c r="C11" s="6">
+        <v>5006</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="1">
+        <v>6</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="71">
   <si>
     <t>_id</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>10级技能书</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>40001</t>
@@ -2457,8 +2460,11 @@
       <c r="E6" s="1">
         <v>4</v>
       </c>
+      <c r="G6" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="H6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2466,16 +2472,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2483,16 +2489,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2500,16 +2506,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2517,16 +2523,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2534,16 +2540,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2551,56 +2557,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2713,16 +2719,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2730,16 +2736,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2747,16 +2753,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2764,16 +2770,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -2781,16 +2787,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -2798,16 +2804,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="72">
   <si>
     <t>_id</t>
   </si>
@@ -365,27 +365,27 @@
     <t>1级装备</t>
   </si>
   <si>
-    <t>200,30,30,30,2,1</t>
+    <t>100,30,30,30,2,1</t>
   </si>
   <si>
     <t>20001,20002,20003,20004,20005,20006</t>
   </si>
   <si>
-    <t>30,200,30,30,2,1</t>
-  </si>
-  <si>
-    <t>30,30,200,30,2,1</t>
-  </si>
-  <si>
-    <t>30,30,30,200,2,1</t>
-  </si>
-  <si>
-    <t>100,100,100,100,5,1</t>
+    <t>30,100,30,30,2,1</t>
+  </si>
+  <si>
+    <t>30,30,100,30,2,1</t>
+  </si>
+  <si>
+    <t>30,30,30,100,2,1</t>
   </si>
   <si>
     <t>100,100,100,100,10,5</t>
   </si>
   <si>
+    <t>100,100,100,100,20,10</t>
+  </si>
+  <si>
     <t>10级装备</t>
   </si>
   <si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>20019,20020,20021,20022,20023,20024</t>
+  </si>
+  <si>
+    <t>100,100,100,100,5,2</t>
   </si>
   <si>
     <t>40级装备</t>
@@ -1984,7 +1987,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>27</v>
@@ -2001,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>27</v>
@@ -2012,7 +2015,7 @@
         <v>2025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -2021,7 +2024,7 @@
         <v>15</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
@@ -2029,7 +2032,7 @@
         <v>2026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
@@ -2038,7 +2041,7 @@
         <v>17</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
@@ -2046,7 +2049,7 @@
         <v>2027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -2055,7 +2058,7 @@
         <v>18</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
@@ -2063,7 +2066,7 @@
         <v>2028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -2072,7 +2075,7 @@
         <v>19</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
@@ -2080,16 +2083,16 @@
         <v>2029</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="1">
-        <v>2</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>20</v>
-      </c>
       <c r="H34" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
@@ -2097,16 +2100,16 @@
         <v>2030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
@@ -2114,7 +2117,7 @@
         <v>2031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -2123,7 +2126,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
@@ -2131,7 +2134,7 @@
         <v>2032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
@@ -2140,7 +2143,7 @@
         <v>17</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
@@ -2148,7 +2151,7 @@
         <v>2033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -2157,7 +2160,7 @@
         <v>18</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
@@ -2165,7 +2168,7 @@
         <v>2034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -2174,7 +2177,7 @@
         <v>19</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
@@ -2182,16 +2185,16 @@
         <v>2035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
@@ -2199,16 +2202,16 @@
         <v>2036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2455,16 +2458,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2472,16 +2475,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2489,16 +2492,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2506,16 +2509,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2523,16 +2526,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2540,16 +2543,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2557,56 +2560,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2719,16 +2722,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2736,16 +2739,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2753,16 +2756,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2770,16 +2773,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -2787,16 +2790,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -2804,16 +2807,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
   <si>
     <t>_id</t>
   </si>
@@ -365,58 +365,115 @@
     <t>1级装备</t>
   </si>
   <si>
-    <t>100,30,30,30,2,1</t>
+    <t>100,30,30,30,10,5</t>
   </si>
   <si>
     <t>20001,20002,20003,20004,20005,20006</t>
   </si>
   <si>
-    <t>30,100,30,30,2,1</t>
-  </si>
-  <si>
-    <t>30,30,100,30,2,1</t>
-  </si>
-  <si>
-    <t>30,30,30,100,2,1</t>
+    <t>30,100,30,30,10,5</t>
+  </si>
+  <si>
+    <t>30,30,100,30,10,5</t>
+  </si>
+  <si>
+    <t>30,30,30,100,10,5</t>
+  </si>
+  <si>
+    <t>100,100,100,100,20,10</t>
+  </si>
+  <si>
+    <t>100,100,100,100,30,15</t>
+  </si>
+  <si>
+    <t>10级装备</t>
+  </si>
+  <si>
+    <t>100,30,30,30,8,4</t>
+  </si>
+  <si>
+    <t>20007,20008,20009,20010,20011,20012</t>
+  </si>
+  <si>
+    <t>30,100,30,30,8,4</t>
+  </si>
+  <si>
+    <t>30,30,100,30,8,4</t>
+  </si>
+  <si>
+    <t>30,30,30,100,8,4</t>
+  </si>
+  <si>
+    <t>100,100,100,100,14,7</t>
+  </si>
+  <si>
+    <t>100,100,100,100,24,12</t>
+  </si>
+  <si>
+    <t>20级装备</t>
+  </si>
+  <si>
+    <t>100,30,30,30,6,3</t>
+  </si>
+  <si>
+    <t>20013,20014,20015,20016,20017,20018</t>
+  </si>
+  <si>
+    <t>30,100,30,30,6,3</t>
+  </si>
+  <si>
+    <t>30,30,100,30,6,3</t>
+  </si>
+  <si>
+    <t>30,30,30,100,6,3</t>
+  </si>
+  <si>
+    <t>100,100,100,100,12,6</t>
+  </si>
+  <si>
+    <t>100,100,100,100,18,9</t>
+  </si>
+  <si>
+    <t>30级装备</t>
+  </si>
+  <si>
+    <t>20019,20020,20021,20022,20023,20024</t>
   </si>
   <si>
     <t>100,100,100,100,10,5</t>
   </si>
   <si>
-    <t>100,100,100,100,20,10</t>
-  </si>
-  <si>
-    <t>10级装备</t>
-  </si>
-  <si>
-    <t>20007,20008,20009,20010,20011,20012</t>
-  </si>
-  <si>
-    <t>20级装备</t>
-  </si>
-  <si>
-    <t>20013,20014,20015,20016,20017,20018</t>
-  </si>
-  <si>
-    <t>30级装备</t>
-  </si>
-  <si>
-    <t>20019,20020,20021,20022,20023,20024</t>
-  </si>
-  <si>
-    <t>100,100,100,100,5,2</t>
+    <t>100,100,100,100,16,8</t>
   </si>
   <si>
     <t>40级装备</t>
   </si>
   <si>
+    <t>100,30,30,30,4,2</t>
+  </si>
+  <si>
     <t>20025,20026,20027,20028,20029,20030</t>
   </si>
   <si>
+    <t>30,100,30,30,4,2</t>
+  </si>
+  <si>
+    <t>30,30,100,30,4,2</t>
+  </si>
+  <si>
+    <t>30,30,30,100,4,2</t>
+  </si>
+  <si>
+    <t>100,100,100,100,8,4</t>
+  </si>
+  <si>
     <t>50级装备</t>
   </si>
   <si>
     <t>20031,20032,20033,20034,20035,20036</t>
+  </si>
+  <si>
+    <t>100,100,100,100,5,3</t>
   </si>
   <si>
     <t>10级技能书</t>
@@ -1715,10 +1772,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
@@ -1732,10 +1789,10 @@
         <v>2</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
@@ -1749,10 +1806,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
@@ -1766,10 +1823,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
@@ -1783,10 +1840,10 @@
         <v>2</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
@@ -1800,10 +1857,10 @@
         <v>2</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:8">
@@ -1811,16 +1868,16 @@
         <v>2013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:8">
@@ -1828,16 +1885,16 @@
         <v>2014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:8">
@@ -1845,16 +1902,16 @@
         <v>2015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
@@ -1862,16 +1919,16 @@
         <v>2016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
@@ -1879,16 +1936,16 @@
         <v>2017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
@@ -1896,16 +1953,16 @@
         <v>2018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
@@ -1913,16 +1970,16 @@
         <v>2019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
@@ -1930,16 +1987,16 @@
         <v>2020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
@@ -1947,16 +2004,16 @@
         <v>2021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
@@ -1964,16 +2021,16 @@
         <v>2022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
@@ -1981,16 +2038,16 @@
         <v>2023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
@@ -1998,16 +2055,16 @@
         <v>2024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
@@ -2015,16 +2072,16 @@
         <v>2025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
@@ -2032,16 +2089,16 @@
         <v>2026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
@@ -2049,16 +2106,16 @@
         <v>2027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
@@ -2066,16 +2123,16 @@
         <v>2028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
@@ -2083,16 +2140,16 @@
         <v>2029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
@@ -2100,16 +2157,16 @@
         <v>2030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
@@ -2117,16 +2174,16 @@
         <v>2031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
@@ -2134,16 +2191,16 @@
         <v>2032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
@@ -2151,16 +2208,16 @@
         <v>2033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
@@ -2168,16 +2225,16 @@
         <v>2034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
@@ -2185,16 +2242,16 @@
         <v>2035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
@@ -2202,16 +2259,16 @@
         <v>2036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2458,16 +2515,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2475,16 +2532,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2492,16 +2549,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2509,16 +2566,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2526,16 +2583,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2543,16 +2600,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2560,56 +2617,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2722,16 +2779,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2739,16 +2796,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2756,16 +2813,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2773,16 +2830,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -2790,16 +2847,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -2807,16 +2864,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="100">
   <si>
     <t>_id</t>
   </si>
@@ -365,19 +365,91 @@
     <t>1级装备</t>
   </si>
   <si>
-    <t>100,30,30,30,10,5</t>
+    <t>100,40,40,40,20,10</t>
   </si>
   <si>
     <t>20001,20002,20003,20004,20005,20006</t>
   </si>
   <si>
-    <t>30,100,30,30,10,5</t>
-  </si>
-  <si>
-    <t>30,30,100,30,10,5</t>
-  </si>
-  <si>
-    <t>30,30,30,100,10,5</t>
+    <t>40,100,40,40,20,10</t>
+  </si>
+  <si>
+    <t>40,40,100,40,20,10</t>
+  </si>
+  <si>
+    <t>40,40,40,100,20,10</t>
+  </si>
+  <si>
+    <t>100,100,100,100,40,20</t>
+  </si>
+  <si>
+    <t>100,100,100,100,60,30</t>
+  </si>
+  <si>
+    <t>10级装备</t>
+  </si>
+  <si>
+    <t>100,40,40,40,16,8</t>
+  </si>
+  <si>
+    <t>20007,20008,20009,20010,20011,20012</t>
+  </si>
+  <si>
+    <t>40,100,40,40,16,8</t>
+  </si>
+  <si>
+    <t>40,40,100,40,16,8</t>
+  </si>
+  <si>
+    <t>40,40,40,100,16,8</t>
+  </si>
+  <si>
+    <t>100,100,100,100,32,16</t>
+  </si>
+  <si>
+    <t>100,100,100,100,48,24</t>
+  </si>
+  <si>
+    <t>20级装备</t>
+  </si>
+  <si>
+    <t>100,40,40,40,12,6</t>
+  </si>
+  <si>
+    <t>20013,20014,20015,20016,20017,20018</t>
+  </si>
+  <si>
+    <t>40,100,40,40,12,6</t>
+  </si>
+  <si>
+    <t>40,40,100,40,12,6</t>
+  </si>
+  <si>
+    <t>40,40,40,100,12,6</t>
+  </si>
+  <si>
+    <t>100,100,100,100,24,12</t>
+  </si>
+  <si>
+    <t>100,100,100,100,36,18</t>
+  </si>
+  <si>
+    <t>30级装备</t>
+  </si>
+  <si>
+    <t>100,40,40,40,10,5</t>
+  </si>
+  <si>
+    <t>20019,20020,20021,20022,20023,20024</t>
+  </si>
+  <si>
+    <t>40,100,40,40,10,5</t>
+  </si>
+  <si>
+    <t>40,40,100,40,10,5</t>
+  </si>
+  <si>
+    <t>40,40,40,100,10,5</t>
   </si>
   <si>
     <t>100,100,100,100,20,10</t>
@@ -386,94 +458,49 @@
     <t>100,100,100,100,30,15</t>
   </si>
   <si>
-    <t>10级装备</t>
-  </si>
-  <si>
-    <t>100,30,30,30,8,4</t>
-  </si>
-  <si>
-    <t>20007,20008,20009,20010,20011,20012</t>
-  </si>
-  <si>
-    <t>30,100,30,30,8,4</t>
-  </si>
-  <si>
-    <t>30,30,100,30,8,4</t>
-  </si>
-  <si>
-    <t>30,30,30,100,8,4</t>
-  </si>
-  <si>
-    <t>100,100,100,100,14,7</t>
-  </si>
-  <si>
-    <t>100,100,100,100,24,12</t>
-  </si>
-  <si>
-    <t>20级装备</t>
-  </si>
-  <si>
-    <t>100,30,30,30,6,3</t>
-  </si>
-  <si>
-    <t>20013,20014,20015,20016,20017,20018</t>
-  </si>
-  <si>
-    <t>30,100,30,30,6,3</t>
-  </si>
-  <si>
-    <t>30,30,100,30,6,3</t>
-  </si>
-  <si>
-    <t>30,30,30,100,6,3</t>
+    <t>40级装备</t>
+  </si>
+  <si>
+    <t>100,40,40,40,8,4</t>
+  </si>
+  <si>
+    <t>20025,20026,20027,20028,20029,20030</t>
+  </si>
+  <si>
+    <t>40,100,40,40,8,4</t>
+  </si>
+  <si>
+    <t>40,40,100,40,8,4</t>
+  </si>
+  <si>
+    <t>40,40,40,100,8,4</t>
+  </si>
+  <si>
+    <t>100,100,100,100,16,8</t>
+  </si>
+  <si>
+    <t>50级装备</t>
+  </si>
+  <si>
+    <t>100,40,40,40,6,3</t>
+  </si>
+  <si>
+    <t>20031,20032,20033,20034,20035,20036</t>
+  </si>
+  <si>
+    <t>40,100,40,40,6,3</t>
+  </si>
+  <si>
+    <t>40,40,100,40,6,3</t>
+  </si>
+  <si>
+    <t>40,40,40,100,6,3</t>
   </si>
   <si>
     <t>100,100,100,100,12,6</t>
   </si>
   <si>
     <t>100,100,100,100,18,9</t>
-  </si>
-  <si>
-    <t>30级装备</t>
-  </si>
-  <si>
-    <t>20019,20020,20021,20022,20023,20024</t>
-  </si>
-  <si>
-    <t>100,100,100,100,10,5</t>
-  </si>
-  <si>
-    <t>100,100,100,100,16,8</t>
-  </si>
-  <si>
-    <t>40级装备</t>
-  </si>
-  <si>
-    <t>100,30,30,30,4,2</t>
-  </si>
-  <si>
-    <t>20025,20026,20027,20028,20029,20030</t>
-  </si>
-  <si>
-    <t>30,100,30,30,4,2</t>
-  </si>
-  <si>
-    <t>30,30,100,30,4,2</t>
-  </si>
-  <si>
-    <t>30,30,30,100,4,2</t>
-  </si>
-  <si>
-    <t>100,100,100,100,8,4</t>
-  </si>
-  <si>
-    <t>50级装备</t>
-  </si>
-  <si>
-    <t>20031,20032,20033,20034,20035,20036</t>
-  </si>
-  <si>
-    <t>100,100,100,100,5,3</t>
   </si>
   <si>
     <t>10级技能书</t>
@@ -1976,10 +2003,10 @@
         <v>2</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
@@ -1993,10 +2020,10 @@
         <v>2</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
@@ -2010,10 +2037,10 @@
         <v>2</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
@@ -2027,10 +2054,10 @@
         <v>2</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
@@ -2044,10 +2071,10 @@
         <v>2</v>
       </c>
       <c r="G28" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
@@ -2061,10 +2088,10 @@
         <v>2</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
@@ -2072,16 +2099,16 @@
         <v>2025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
@@ -2089,16 +2116,16 @@
         <v>2026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
@@ -2106,16 +2133,16 @@
         <v>2027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
@@ -2123,16 +2150,16 @@
         <v>2028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
@@ -2140,16 +2167,16 @@
         <v>2029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="G34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
@@ -2157,16 +2184,16 @@
         <v>2030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
@@ -2174,16 +2201,16 @@
         <v>2031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
@@ -2191,16 +2218,16 @@
         <v>2032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
@@ -2208,16 +2235,16 @@
         <v>2033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
@@ -2225,16 +2252,16 @@
         <v>2034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
@@ -2242,16 +2269,16 @@
         <v>2035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
@@ -2259,16 +2286,16 @@
         <v>2036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2515,16 +2542,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2532,16 +2559,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2549,16 +2576,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2566,16 +2593,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2583,16 +2610,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2600,16 +2627,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2617,56 +2644,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2779,16 +2806,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2796,16 +2823,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2813,16 +2840,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2830,16 +2857,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -2847,16 +2874,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -2864,16 +2891,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -318,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="112">
   <si>
     <t>_id</t>
   </si>
@@ -501,6 +506,42 @@
   </si>
   <si>
     <t>100,100,100,100,18,9</t>
+  </si>
+  <si>
+    <t>神兵符1-2</t>
+  </si>
+  <si>
+    <t>100,10</t>
+  </si>
+  <si>
+    <t>5015,5016</t>
+  </si>
+  <si>
+    <t>神兵符1-3</t>
+  </si>
+  <si>
+    <t>100,10,1</t>
+  </si>
+  <si>
+    <t>5015,5016,5017</t>
+  </si>
+  <si>
+    <t>神兵符1-4</t>
+  </si>
+  <si>
+    <t>100,30,10,1</t>
+  </si>
+  <si>
+    <t>5015,5016,5017,5018</t>
+  </si>
+  <si>
+    <t>神兵符1-5</t>
+  </si>
+  <si>
+    <t>100,30,10,5,1</t>
+  </si>
+  <si>
+    <t>5015,5016,5017,5018,5019</t>
   </si>
   <si>
     <t>10级技能书</t>
@@ -808,12 +849,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2314,7 +2355,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H32"/>
+  <dimension ref="C1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -2393,14 +2434,83 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1"/>
+    <row r="6" customHeight="1" spans="3:8">
+      <c r="C6" s="1">
+        <v>3001</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:8">
+      <c r="C7" s="1">
+        <v>3002</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:8">
+      <c r="C8" s="1">
+        <v>3003</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:8">
+      <c r="C9" s="1">
+        <v>3004</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
     <row r="10" customHeight="1" spans="3:8">
       <c r="G10" s="8"/>
     </row>
-    <row r="11" customHeight="1" spans="3:8">
-      <c r="G11" s="8"/>
-    </row>
-    <row r="16" ht="32" customHeight="1"/>
+    <row r="15" ht="32" customHeight="1"/>
+    <row r="23" customHeight="1" spans="3:8">
+      <c r="C23" s="6"/>
+      <c r="H23" s="1"/>
+    </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="6"/>
       <c r="H24" s="1"/>
@@ -2427,17 +2537,13 @@
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="6"/>
+      <c r="G30" s="7"/>
       <c r="H30" s="1"/>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="6"/>
       <c r="G31" s="7"/>
       <c r="H31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:8">
-      <c r="C32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2542,16 +2648,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2559,16 +2665,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2576,16 +2682,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2593,16 +2699,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2610,16 +2716,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2627,16 +2733,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2644,56 +2750,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2806,16 +2912,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2823,16 +2929,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2840,16 +2946,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2857,16 +2963,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -2874,16 +2980,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -2891,16 +2997,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -514,7 +514,7 @@
     <t>100,10</t>
   </si>
   <si>
-    <t>5015,5016</t>
+    <t>11,12</t>
   </si>
   <si>
     <t>神兵符1-3</t>
@@ -523,7 +523,7 @@
     <t>100,10,1</t>
   </si>
   <si>
-    <t>5015,5016,5017</t>
+    <t>11,12,13</t>
   </si>
   <si>
     <t>神兵符1-4</t>
@@ -532,7 +532,7 @@
     <t>100,30,10,1</t>
   </si>
   <si>
-    <t>5015,5016,5017,5018</t>
+    <t>11,12,13,14</t>
   </si>
   <si>
     <t>神兵符1-5</t>
@@ -541,7 +541,7 @@
     <t>100,30,10,5,1</t>
   </si>
   <si>
-    <t>5015,5016,5017,5018,5019</t>
+    <t>11,12,13,14,15</t>
   </si>
   <si>
     <t>10级技能书</t>
@@ -849,12 +849,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2495,7 +2495,6 @@
       <c r="E9" s="1">
         <v>5</v>
       </c>
-      <c r="F9" s="1"/>
       <c r="G9" s="10" t="s">
         <v>71</v>
       </c>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="136">
   <si>
     <t>_id</t>
   </si>
@@ -508,6 +508,42 @@
     <t>100,100,100,100,18,9</t>
   </si>
   <si>
+    <t>60级装备</t>
+  </si>
+  <si>
+    <t>100,40,40,40,5,2</t>
+  </si>
+  <si>
+    <t>20037,20038,20039,20040,20041,20042</t>
+  </si>
+  <si>
+    <t>40,100,40,40,5,2</t>
+  </si>
+  <si>
+    <t>40,40,100,40,5,2</t>
+  </si>
+  <si>
+    <t>40,40,40,100,5,2</t>
+  </si>
+  <si>
+    <t>100,100,100,100,10,5</t>
+  </si>
+  <si>
+    <t>100,100,100,100,15,8</t>
+  </si>
+  <si>
+    <t>70级装备</t>
+  </si>
+  <si>
+    <t>20043,20044,20045,20046,20047,20048</t>
+  </si>
+  <si>
+    <t>80级装备</t>
+  </si>
+  <si>
+    <t>20049,20050,20051,20052,20053,20054</t>
+  </si>
+  <si>
     <t>神兵符1-2</t>
   </si>
   <si>
@@ -655,10 +691,46 @@
     <t>50013,50014,50015</t>
   </si>
   <si>
-    <t>熔火地穴珍宝材料</t>
+    <t>蛮鬃林地珍宝材料</t>
   </si>
   <si>
     <t>50016,50017,50018</t>
+  </si>
+  <si>
+    <t>熔岩地穴珍宝材料</t>
+  </si>
+  <si>
+    <t>50019,50020,50021</t>
+  </si>
+  <si>
+    <t>冰封王陵珍宝材料</t>
+  </si>
+  <si>
+    <t>50022,50023,50024</t>
+  </si>
+  <si>
+    <t>暗影祭坛珍宝材料</t>
+  </si>
+  <si>
+    <t>50025,50026,50027</t>
+  </si>
+  <si>
+    <t>蛮族之地珍宝材料</t>
+  </si>
+  <si>
+    <t>50028,50029,50030</t>
+  </si>
+  <si>
+    <t>虚空裂谷珍宝材料</t>
+  </si>
+  <si>
+    <t>50031,50032,50033</t>
+  </si>
+  <si>
+    <t>地狱烈焰珍宝材料</t>
+  </si>
+  <si>
+    <t>50034,50035,50036</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1724,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:H41"/>
+  <dimension ref="C2:H59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -2337,6 +2409,312 @@
       </c>
       <c r="H41" s="9" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:8">
+      <c r="C42" s="1">
+        <v>2037</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:8">
+      <c r="C43" s="1">
+        <v>2038</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:8">
+      <c r="C44" s="1">
+        <v>2039</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:8">
+      <c r="C45" s="1">
+        <v>2040</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:8">
+      <c r="C46" s="1">
+        <v>2041</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:8">
+      <c r="C47" s="1">
+        <v>2042</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:8">
+      <c r="C48" s="1">
+        <v>2043</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="1">
+        <v>2</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:8">
+      <c r="C49" s="1">
+        <v>2044</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="1">
+        <v>2</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:8">
+      <c r="C50" s="1">
+        <v>2045</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:8">
+      <c r="C51" s="1">
+        <v>2046</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:8">
+      <c r="C52" s="1">
+        <v>2047</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="1">
+        <v>2</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:8">
+      <c r="C53" s="1">
+        <v>2048</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:8">
+      <c r="C54" s="1">
+        <v>2049</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:8">
+      <c r="C55" s="1">
+        <v>2050</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:8">
+      <c r="C56" s="1">
+        <v>2051</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:8">
+      <c r="C57" s="1">
+        <v>2052</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:8">
+      <c r="C58" s="1">
+        <v>2053</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:8">
+      <c r="C59" s="1">
+        <v>2054</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="1">
+        <v>2</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2439,16 +2817,16 @@
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:8">
@@ -2456,16 +2834,16 @@
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2473,16 +2851,16 @@
         <v>3003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2490,16 +2868,16 @@
         <v>3004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -2647,16 +3025,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2664,16 +3042,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2681,16 +3059,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2698,16 +3076,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2715,16 +3093,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2732,16 +3110,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -2749,56 +3127,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -2827,7 +3205,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H11"/>
+  <dimension ref="C1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -2911,16 +3289,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -2928,16 +3306,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2945,16 +3323,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2962,16 +3340,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -2979,16 +3357,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -2996,16 +3374,118 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>111</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:8">
+      <c r="C12" s="6">
+        <v>5007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:8">
+      <c r="C13" s="6">
+        <v>5008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="1">
+        <v>6</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:8">
+      <c r="C14" s="6">
+        <v>5009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="1">
+        <v>6</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:8">
+      <c r="C15" s="6">
+        <v>5010</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:8">
+      <c r="C16" s="6">
+        <v>5011</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="1">
+        <v>6</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:8">
+      <c r="C17" s="6">
+        <v>5012</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="1">
+        <v>6</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowWidth="25600" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="142">
   <si>
     <t>_id</t>
   </si>
@@ -542,6 +542,24 @@
   </si>
   <si>
     <t>20049,20050,20051,20052,20053,20054</t>
+  </si>
+  <si>
+    <t>90级装备</t>
+  </si>
+  <si>
+    <t>20055,20056,20057,20058,20059,20060</t>
+  </si>
+  <si>
+    <t>100级装备</t>
+  </si>
+  <si>
+    <t>20061,20062,20063,20064,20065,20066</t>
+  </si>
+  <si>
+    <t>110级装备</t>
+  </si>
+  <si>
+    <t>20067,20068,20069,20070,20071,20072</t>
   </si>
   <si>
     <t>神兵符1-2</t>
@@ -1724,7 +1742,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:H59"/>
+  <dimension ref="C2:H77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -2715,6 +2733,312 @@
       </c>
       <c r="H59" s="9" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:8">
+      <c r="C60" s="1">
+        <v>2055</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="1">
+        <v>2</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:8">
+      <c r="C61" s="1">
+        <v>2056</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:8">
+      <c r="C62" s="1">
+        <v>2057</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="1">
+        <v>2</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:8">
+      <c r="C63" s="1">
+        <v>2058</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:8">
+      <c r="C64" s="1">
+        <v>2059</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:8">
+      <c r="C65" s="1">
+        <v>2060</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:8">
+      <c r="C66" s="1">
+        <v>2061</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66" s="1">
+        <v>2</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:8">
+      <c r="C67" s="1">
+        <v>2062</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:8">
+      <c r="C68" s="1">
+        <v>2063</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:8">
+      <c r="C69" s="1">
+        <v>2064</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:8">
+      <c r="C70" s="1">
+        <v>2065</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:8">
+      <c r="C71" s="1">
+        <v>2066</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:8">
+      <c r="C72" s="1">
+        <v>2067</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:8">
+      <c r="C73" s="1">
+        <v>2068</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E73" s="1">
+        <v>2</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:8">
+      <c r="C74" s="1">
+        <v>2069</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E74" s="1">
+        <v>2</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:8">
+      <c r="C75" s="1">
+        <v>2070</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E75" s="1">
+        <v>2</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:8">
+      <c r="C76" s="1">
+        <v>2071</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E76" s="1">
+        <v>2</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:8">
+      <c r="C77" s="1">
+        <v>2072</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E77" s="1">
+        <v>2</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2817,16 +3141,16 @@
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:8">
@@ -2834,16 +3158,16 @@
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -2851,16 +3175,16 @@
         <v>3003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -2868,16 +3192,16 @@
         <v>3004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3025,16 +3349,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3042,16 +3366,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3059,16 +3383,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3076,16 +3400,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3093,16 +3417,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3110,16 +3434,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3127,56 +3451,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -3289,16 +3613,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -3306,16 +3630,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3323,16 +3647,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3340,16 +3664,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3357,16 +3681,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -3374,16 +3698,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:8">
@@ -3391,16 +3715,16 @@
         <v>5007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
@@ -3408,16 +3732,16 @@
         <v>5008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
@@ -3425,16 +3749,16 @@
         <v>5009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
@@ -3442,16 +3766,16 @@
         <v>5010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
@@ -3459,16 +3783,16 @@
         <v>5011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
@@ -3476,16 +3800,16 @@
         <v>5012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="125">
   <si>
     <t>_id</t>
   </si>
@@ -466,70 +466,19 @@
     <t>40级装备</t>
   </si>
   <si>
-    <t>100,40,40,40,8,4</t>
-  </si>
-  <si>
     <t>20025,20026,20027,20028,20029,20030</t>
   </si>
   <si>
-    <t>40,100,40,40,8,4</t>
-  </si>
-  <si>
-    <t>40,40,100,40,8,4</t>
-  </si>
-  <si>
-    <t>40,40,40,100,8,4</t>
-  </si>
-  <si>
-    <t>100,100,100,100,16,8</t>
-  </si>
-  <si>
     <t>50级装备</t>
   </si>
   <si>
-    <t>100,40,40,40,6,3</t>
-  </si>
-  <si>
     <t>20031,20032,20033,20034,20035,20036</t>
   </si>
   <si>
-    <t>40,100,40,40,6,3</t>
-  </si>
-  <si>
-    <t>40,40,100,40,6,3</t>
-  </si>
-  <si>
-    <t>40,40,40,100,6,3</t>
-  </si>
-  <si>
-    <t>100,100,100,100,12,6</t>
-  </si>
-  <si>
-    <t>100,100,100,100,18,9</t>
-  </si>
-  <si>
     <t>60级装备</t>
   </si>
   <si>
-    <t>100,40,40,40,5,2</t>
-  </si>
-  <si>
     <t>20037,20038,20039,20040,20041,20042</t>
-  </si>
-  <si>
-    <t>40,100,40,40,5,2</t>
-  </si>
-  <si>
-    <t>40,40,100,40,5,2</t>
-  </si>
-  <si>
-    <t>40,40,40,100,5,2</t>
-  </si>
-  <si>
-    <t>100,100,100,100,10,5</t>
-  </si>
-  <si>
-    <t>100,100,100,100,15,8</t>
   </si>
   <si>
     <t>70级装备</t>
@@ -939,12 +888,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2236,10 +2185,10 @@
         <v>2</v>
       </c>
       <c r="G30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
@@ -2253,10 +2202,10 @@
         <v>2</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
@@ -2270,10 +2219,10 @@
         <v>2</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
@@ -2287,10 +2236,10 @@
         <v>2</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
@@ -2304,10 +2253,10 @@
         <v>2</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
@@ -2321,10 +2270,10 @@
         <v>2</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
@@ -2332,16 +2281,16 @@
         <v>2031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
@@ -2349,16 +2298,16 @@
         <v>2032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
@@ -2366,16 +2315,16 @@
         <v>2033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
@@ -2383,16 +2332,16 @@
         <v>2034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
@@ -2400,16 +2349,16 @@
         <v>2035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
@@ -2417,16 +2366,16 @@
         <v>2036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
@@ -2434,16 +2383,16 @@
         <v>2037</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
@@ -2451,16 +2400,16 @@
         <v>2038</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
@@ -2468,16 +2417,16 @@
         <v>2039</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
@@ -2485,16 +2434,16 @@
         <v>2040</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
@@ -2502,16 +2451,16 @@
         <v>2041</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
@@ -2519,16 +2468,16 @@
         <v>2042</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
@@ -2536,16 +2485,16 @@
         <v>2043</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
@@ -2553,16 +2502,16 @@
         <v>2044</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
@@ -2570,16 +2519,16 @@
         <v>2045</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
@@ -2587,16 +2536,16 @@
         <v>2046</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
@@ -2604,16 +2553,16 @@
         <v>2047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
@@ -2621,16 +2570,16 @@
         <v>2048</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
@@ -2638,16 +2587,16 @@
         <v>2049</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
@@ -2655,16 +2604,16 @@
         <v>2050</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
@@ -2672,16 +2621,16 @@
         <v>2051</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
@@ -2689,16 +2638,16 @@
         <v>2052</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
@@ -2706,16 +2655,16 @@
         <v>2053</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
@@ -2723,16 +2672,16 @@
         <v>2054</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
@@ -2740,16 +2689,16 @@
         <v>2055</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
@@ -2757,16 +2706,16 @@
         <v>2056</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
@@ -2774,16 +2723,16 @@
         <v>2057</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
@@ -2791,16 +2740,16 @@
         <v>2058</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
@@ -2808,16 +2757,16 @@
         <v>2059</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
@@ -2825,16 +2774,16 @@
         <v>2060</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
@@ -2842,16 +2791,16 @@
         <v>2061</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
@@ -2859,16 +2808,16 @@
         <v>2062</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
@@ -2876,16 +2825,16 @@
         <v>2063</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
@@ -2893,16 +2842,16 @@
         <v>2064</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
@@ -2910,16 +2859,16 @@
         <v>2065</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
@@ -2927,16 +2876,16 @@
         <v>2066</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
@@ -2944,16 +2893,16 @@
         <v>2067</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
@@ -2961,16 +2910,16 @@
         <v>2068</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
@@ -2978,16 +2927,16 @@
         <v>2069</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
@@ -2995,16 +2944,16 @@
         <v>2070</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
@@ -3012,16 +2961,16 @@
         <v>2071</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
@@ -3029,16 +2978,16 @@
         <v>2072</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3141,16 +3090,16 @@
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:8">
@@ -3158,16 +3107,16 @@
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3175,16 +3124,16 @@
         <v>3003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3192,16 +3141,16 @@
         <v>3004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3349,16 +3298,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3366,16 +3315,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3383,16 +3332,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3400,16 +3349,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3417,16 +3366,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3434,16 +3383,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3451,56 +3400,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -3613,16 +3562,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -3630,16 +3579,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3647,16 +3596,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3664,16 +3613,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3681,16 +3630,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -3698,16 +3647,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:8">
@@ -3715,16 +3664,16 @@
         <v>5007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
@@ -3732,16 +3681,16 @@
         <v>5008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
@@ -3749,16 +3698,16 @@
         <v>5009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="G14" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
@@ -3766,16 +3715,16 @@
         <v>5010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
@@ -3783,16 +3732,16 @@
         <v>5011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
@@ -3800,16 +3749,16 @@
         <v>5012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="127">
   <si>
     <t>_id</t>
   </si>
@@ -469,10 +469,16 @@
     <t>20025,20026,20027,20028,20029,20030</t>
   </si>
   <si>
+    <t>100,100,100,100,25,15</t>
+  </si>
+  <si>
     <t>50级装备</t>
   </si>
   <si>
     <t>20031,20032,20033,20034,20035,20036</t>
+  </si>
+  <si>
+    <t>100,100,100,100,20,15</t>
   </si>
   <si>
     <t>60级装备</t>
@@ -888,12 +894,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2270,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>47</v>
@@ -2281,7 +2287,7 @@
         <v>2031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -2290,7 +2296,7 @@
         <v>39</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
@@ -2298,7 +2304,7 @@
         <v>2032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
@@ -2307,7 +2313,7 @@
         <v>41</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
@@ -2315,7 +2321,7 @@
         <v>2033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -2324,7 +2330,7 @@
         <v>42</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
@@ -2332,7 +2338,7 @@
         <v>2034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -2341,7 +2347,7 @@
         <v>43</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
@@ -2349,7 +2355,7 @@
         <v>2035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -2358,7 +2364,7 @@
         <v>44</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
@@ -2366,16 +2372,16 @@
         <v>2036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
@@ -2383,7 +2389,7 @@
         <v>2037</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -2392,7 +2398,7 @@
         <v>39</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
@@ -2400,7 +2406,7 @@
         <v>2038</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -2409,7 +2415,7 @@
         <v>41</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
@@ -2417,7 +2423,7 @@
         <v>2039</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
@@ -2426,7 +2432,7 @@
         <v>42</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
@@ -2434,7 +2440,7 @@
         <v>2040</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
@@ -2443,7 +2449,7 @@
         <v>43</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
@@ -2451,7 +2457,7 @@
         <v>2041</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
@@ -2460,7 +2466,7 @@
         <v>44</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
@@ -2468,16 +2474,16 @@
         <v>2042</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
@@ -2485,7 +2491,7 @@
         <v>2043</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
@@ -2494,7 +2500,7 @@
         <v>39</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
@@ -2502,7 +2508,7 @@
         <v>2044</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
@@ -2511,7 +2517,7 @@
         <v>41</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
@@ -2519,7 +2525,7 @@
         <v>2045</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
@@ -2528,7 +2534,7 @@
         <v>42</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
@@ -2536,7 +2542,7 @@
         <v>2046</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
@@ -2545,7 +2551,7 @@
         <v>43</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
@@ -2553,7 +2559,7 @@
         <v>2047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
@@ -2562,7 +2568,7 @@
         <v>44</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
@@ -2570,16 +2576,16 @@
         <v>2048</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
@@ -2587,7 +2593,7 @@
         <v>2049</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
@@ -2596,7 +2602,7 @@
         <v>39</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
@@ -2604,7 +2610,7 @@
         <v>2050</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
@@ -2613,7 +2619,7 @@
         <v>41</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
@@ -2621,7 +2627,7 @@
         <v>2051</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
@@ -2630,7 +2636,7 @@
         <v>42</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
@@ -2638,7 +2644,7 @@
         <v>2052</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
@@ -2647,7 +2653,7 @@
         <v>43</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
@@ -2655,7 +2661,7 @@
         <v>2053</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
@@ -2664,7 +2670,7 @@
         <v>44</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
@@ -2672,16 +2678,16 @@
         <v>2054</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
@@ -2689,7 +2695,7 @@
         <v>2055</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
@@ -2698,7 +2704,7 @@
         <v>39</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
@@ -2706,7 +2712,7 @@
         <v>2056</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
@@ -2715,7 +2721,7 @@
         <v>41</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
@@ -2723,7 +2729,7 @@
         <v>2057</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
@@ -2732,7 +2738,7 @@
         <v>42</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
@@ -2740,7 +2746,7 @@
         <v>2058</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
@@ -2749,7 +2755,7 @@
         <v>43</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
@@ -2757,7 +2763,7 @@
         <v>2059</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
@@ -2766,7 +2772,7 @@
         <v>44</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
@@ -2774,16 +2780,16 @@
         <v>2060</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
@@ -2791,7 +2797,7 @@
         <v>2061</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
@@ -2800,7 +2806,7 @@
         <v>39</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
@@ -2808,7 +2814,7 @@
         <v>2062</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
@@ -2817,7 +2823,7 @@
         <v>41</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
@@ -2825,7 +2831,7 @@
         <v>2063</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
@@ -2834,7 +2840,7 @@
         <v>42</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
@@ -2842,7 +2848,7 @@
         <v>2064</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -2851,7 +2857,7 @@
         <v>43</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
@@ -2859,7 +2865,7 @@
         <v>2065</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -2868,7 +2874,7 @@
         <v>44</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
@@ -2876,16 +2882,16 @@
         <v>2066</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
@@ -2893,7 +2899,7 @@
         <v>2067</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -2902,7 +2908,7 @@
         <v>39</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
@@ -2910,7 +2916,7 @@
         <v>2068</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -2919,7 +2925,7 @@
         <v>41</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
@@ -2927,7 +2933,7 @@
         <v>2069</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -2936,7 +2942,7 @@
         <v>42</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
@@ -2944,7 +2950,7 @@
         <v>2070</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -2953,7 +2959,7 @@
         <v>43</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
@@ -2961,7 +2967,7 @@
         <v>2071</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
@@ -2970,7 +2976,7 @@
         <v>44</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
@@ -2978,16 +2984,16 @@
         <v>2072</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3090,16 +3096,16 @@
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:8">
@@ -3107,16 +3113,16 @@
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3124,16 +3130,16 @@
         <v>3003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3141,16 +3147,16 @@
         <v>3004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3298,16 +3304,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3315,16 +3321,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3332,16 +3338,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3349,16 +3355,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3366,16 +3372,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3383,16 +3389,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3400,56 +3406,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -3562,16 +3568,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -3579,16 +3585,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3596,16 +3602,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3613,16 +3619,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3630,16 +3636,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -3647,16 +3653,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:8">
@@ -3664,16 +3670,16 @@
         <v>5007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
@@ -3681,16 +3687,16 @@
         <v>5008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
@@ -3698,16 +3704,16 @@
         <v>5009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
@@ -3715,16 +3721,16 @@
         <v>5010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
@@ -3732,16 +3738,16 @@
         <v>5011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
@@ -3749,16 +3755,16 @@
         <v>5012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -3012,8 +3012,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="C1:H23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -3162,44 +3162,43 @@
     <row r="10" customHeight="1" spans="3:8">
       <c r="G10" s="8"/>
     </row>
-    <row r="15" ht="32" customHeight="1"/>
+    <row r="15" customHeight="1" spans="3:8">
+      <c r="C15" s="6"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:8">
+      <c r="C16" s="6"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:8">
+      <c r="C17" s="6"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:8">
+      <c r="C18" s="6"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:8">
+      <c r="C19" s="6"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:8">
+      <c r="C20" s="6"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:8">
+      <c r="C21" s="6"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:8">
+      <c r="C22" s="6"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="1"/>
+    </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="6"/>
+      <c r="G23" s="7"/>
       <c r="H23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="3:8">
-      <c r="C24" s="6"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:8">
-      <c r="C25" s="6"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:8">
-      <c r="C26" s="6"/>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="3:8">
-      <c r="C27" s="6"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="3:8">
-      <c r="C28" s="6"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="3:8">
-      <c r="C29" s="6"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="3:8">
-      <c r="C30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:8">
-      <c r="C31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="107">
   <si>
     <t>_id</t>
   </si>
@@ -370,115 +370,55 @@
     <t>1级装备</t>
   </si>
   <si>
-    <t>100,40,40,40,20,10</t>
+    <t>100,40,40,40,10,5</t>
   </si>
   <si>
     <t>20001,20002,20003,20004,20005,20006</t>
   </si>
   <si>
-    <t>40,100,40,40,20,10</t>
-  </si>
-  <si>
-    <t>40,40,100,40,20,10</t>
-  </si>
-  <si>
-    <t>40,40,40,100,20,10</t>
-  </si>
-  <si>
-    <t>100,100,100,100,40,20</t>
-  </si>
-  <si>
-    <t>100,100,100,100,60,30</t>
+    <t>40,100,40,40,10,10</t>
+  </si>
+  <si>
+    <t>40,40,100,40,15,15</t>
+  </si>
+  <si>
+    <t>40,40,40,100,20,20</t>
+  </si>
+  <si>
+    <t>100,100,100,100,25,25</t>
+  </si>
+  <si>
+    <t>100,100,100,100,30,30</t>
   </si>
   <si>
     <t>10级装备</t>
   </si>
   <si>
-    <t>100,40,40,40,16,8</t>
-  </si>
-  <si>
     <t>20007,20008,20009,20010,20011,20012</t>
   </si>
   <si>
-    <t>40,100,40,40,16,8</t>
-  </si>
-  <si>
-    <t>40,40,100,40,16,8</t>
-  </si>
-  <si>
-    <t>40,40,40,100,16,8</t>
-  </si>
-  <si>
-    <t>100,100,100,100,32,16</t>
-  </si>
-  <si>
-    <t>100,100,100,100,48,24</t>
-  </si>
-  <si>
     <t>20级装备</t>
   </si>
   <si>
-    <t>100,40,40,40,12,6</t>
-  </si>
-  <si>
     <t>20013,20014,20015,20016,20017,20018</t>
   </si>
   <si>
-    <t>40,100,40,40,12,6</t>
-  </si>
-  <si>
-    <t>40,40,100,40,12,6</t>
-  </si>
-  <si>
-    <t>40,40,40,100,12,6</t>
-  </si>
-  <si>
-    <t>100,100,100,100,24,12</t>
-  </si>
-  <si>
-    <t>100,100,100,100,36,18</t>
-  </si>
-  <si>
     <t>30级装备</t>
   </si>
   <si>
-    <t>100,40,40,40,10,5</t>
-  </si>
-  <si>
     <t>20019,20020,20021,20022,20023,20024</t>
   </si>
   <si>
-    <t>40,100,40,40,10,5</t>
-  </si>
-  <si>
-    <t>40,40,100,40,10,5</t>
-  </si>
-  <si>
-    <t>40,40,40,100,10,5</t>
-  </si>
-  <si>
-    <t>100,100,100,100,20,10</t>
-  </si>
-  <si>
-    <t>100,100,100,100,30,15</t>
-  </si>
-  <si>
     <t>40级装备</t>
   </si>
   <si>
     <t>20025,20026,20027,20028,20029,20030</t>
   </si>
   <si>
-    <t>100,100,100,100,25,15</t>
-  </si>
-  <si>
     <t>50级装备</t>
   </si>
   <si>
     <t>20031,20032,20033,20034,20035,20036</t>
-  </si>
-  <si>
-    <t>100,100,100,100,20,15</t>
   </si>
   <si>
     <t>60级装备</t>
@@ -894,12 +834,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1885,10 +1825,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
@@ -1902,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
@@ -1919,10 +1859,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
@@ -1936,10 +1876,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
@@ -1953,10 +1893,10 @@
         <v>2</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
@@ -1970,10 +1910,10 @@
         <v>2</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:8">
@@ -1981,16 +1921,16 @@
         <v>2013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:8">
@@ -1998,16 +1938,16 @@
         <v>2014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:8">
@@ -2015,16 +1955,16 @@
         <v>2015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
@@ -2032,16 +1972,16 @@
         <v>2016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
@@ -2049,16 +1989,16 @@
         <v>2017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
@@ -2066,16 +2006,16 @@
         <v>2018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
@@ -2083,16 +2023,16 @@
         <v>2019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
@@ -2100,16 +2040,16 @@
         <v>2020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
@@ -2117,16 +2057,16 @@
         <v>2021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
@@ -2134,16 +2074,16 @@
         <v>2022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
@@ -2151,16 +2091,16 @@
         <v>2023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
@@ -2168,16 +2108,16 @@
         <v>2024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
@@ -2185,16 +2125,16 @@
         <v>2025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
@@ -2202,16 +2142,16 @@
         <v>2026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
@@ -2219,16 +2159,16 @@
         <v>2027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
@@ -2236,16 +2176,16 @@
         <v>2028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
@@ -2253,16 +2193,16 @@
         <v>2029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
@@ -2270,16 +2210,16 @@
         <v>2030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
@@ -2287,16 +2227,16 @@
         <v>2031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
@@ -2304,16 +2244,16 @@
         <v>2032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
@@ -2321,16 +2261,16 @@
         <v>2033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
@@ -2338,16 +2278,16 @@
         <v>2034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
@@ -2355,16 +2295,16 @@
         <v>2035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
@@ -2372,16 +2312,16 @@
         <v>2036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
@@ -2389,16 +2329,16 @@
         <v>2037</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
@@ -2406,16 +2346,16 @@
         <v>2038</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
@@ -2423,16 +2363,16 @@
         <v>2039</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
@@ -2440,16 +2380,16 @@
         <v>2040</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
@@ -2457,16 +2397,16 @@
         <v>2041</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
@@ -2474,16 +2414,16 @@
         <v>2042</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
@@ -2491,16 +2431,16 @@
         <v>2043</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
@@ -2508,16 +2448,16 @@
         <v>2044</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
@@ -2525,16 +2465,16 @@
         <v>2045</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
@@ -2542,16 +2482,16 @@
         <v>2046</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
@@ -2559,16 +2499,16 @@
         <v>2047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
@@ -2576,16 +2516,16 @@
         <v>2048</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
@@ -2593,16 +2533,16 @@
         <v>2049</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
@@ -2610,16 +2550,16 @@
         <v>2050</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
@@ -2627,16 +2567,16 @@
         <v>2051</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
@@ -2644,16 +2584,16 @@
         <v>2052</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
@@ -2661,16 +2601,16 @@
         <v>2053</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
@@ -2678,16 +2618,16 @@
         <v>2054</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
@@ -2695,16 +2635,16 @@
         <v>2055</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="G60" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
@@ -2712,16 +2652,16 @@
         <v>2056</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
@@ -2729,16 +2669,16 @@
         <v>2057</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
@@ -2746,16 +2686,16 @@
         <v>2058</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
@@ -2763,16 +2703,16 @@
         <v>2059</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
@@ -2780,16 +2720,16 @@
         <v>2060</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
@@ -2797,16 +2737,16 @@
         <v>2061</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
@@ -2814,16 +2754,16 @@
         <v>2062</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
@@ -2831,16 +2771,16 @@
         <v>2063</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
@@ -2848,16 +2788,16 @@
         <v>2064</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
@@ -2865,16 +2805,16 @@
         <v>2065</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
@@ -2882,16 +2822,16 @@
         <v>2066</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
@@ -2899,16 +2839,16 @@
         <v>2067</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
@@ -2916,16 +2856,16 @@
         <v>2068</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
@@ -2933,16 +2873,16 @@
         <v>2069</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
@@ -2950,16 +2890,16 @@
         <v>2070</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
@@ -2967,16 +2907,16 @@
         <v>2071</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
@@ -2984,16 +2924,16 @@
         <v>2072</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3096,16 +3036,16 @@
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:8">
@@ -3113,16 +3053,16 @@
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3130,16 +3070,16 @@
         <v>3003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3147,16 +3087,16 @@
         <v>3004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3303,16 +3243,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3320,16 +3260,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3337,16 +3277,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3354,16 +3294,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3371,16 +3311,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3388,16 +3328,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3405,56 +3345,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -3567,16 +3507,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -3584,16 +3524,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3601,16 +3541,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3618,16 +3558,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3635,16 +3575,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -3652,16 +3592,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:8">
@@ -3669,16 +3609,16 @@
         <v>5007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
@@ -3686,16 +3626,16 @@
         <v>5008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
@@ -3703,16 +3643,16 @@
         <v>5009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
@@ -3720,16 +3660,16 @@
         <v>5010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
@@ -3737,16 +3677,16 @@
         <v>5011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
@@ -3754,16 +3694,16 @@
         <v>5012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
